--- a/output/full_scan/batch_seq6_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6438</v>
+        <v>6225</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>618.6067864313409</v>
+        <v>657.4762881015786</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>151</v>
+        <v>59.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.19483006345361</v>
+        <v>67.42976435018691</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.25111738375986</v>
+        <v>51.8201513849315</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.327848704847906</v>
+        <v>1.078394137815737</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.9605244132881998</v>
+        <v>1.884597247182206</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6284</v>
+        <v>6438</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>608.0648281424041</v>
+        <v>618.6067864313409</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>151</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>53.14340517031061</v>
+        <v>57.19483006345361</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.02257106718804</v>
+        <v>14.25111738375986</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.897662852765586</v>
+        <v>2.327848704847906</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.005026002669722</v>
+        <v>0.9605244132881998</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6290</v>
+        <v>6284</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>605.9113494879764</v>
+        <v>608.0648281424041</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>248</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.82341983742649</v>
+        <v>53.14340517031061</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.26214737873338</v>
+        <v>17.02257106718804</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.191134948797634</v>
+        <v>2.897662852765586</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>6.567802564555347</v>
+        <v>1.005026002669722</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6426</v>
+        <v>6290</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>594.8068496958571</v>
+        <v>605.9113494879764</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>263.5</v>
+        <v>248</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>67.11578250326315</v>
+        <v>57.82341983742649</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.47468482274172</v>
+        <v>25.26214737873338</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.125632550007205</v>
+        <v>1.191134948797634</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4.055744527284368</v>
+        <v>6.567802564555347</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6265</v>
+        <v>6426</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>579.9118456708223</v>
+        <v>594.8068496958571</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.1</v>
+        <v>263.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.78109223899119</v>
+        <v>67.11578250326315</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.97010456817325</v>
+        <v>32.47468482274172</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4528480115497993</v>
+        <v>1.125632550007205</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.18951666906253</v>
+        <v>4.055744527284368</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6456</v>
+        <v>6265</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>570.542626497388</v>
+        <v>579.9118456708223</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>74.3</v>
+        <v>57.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.74696784082273</v>
+        <v>52.78109223899119</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.35610190823388</v>
+        <v>22.97010456817325</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.564407789822586</v>
+        <v>0.4528480115497993</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.976940995894704</v>
+        <v>-0.18951666906253</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6435</v>
+        <v>6456</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>565.3622245638517</v>
+        <v>570.542626497388</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>260</v>
+        <v>74.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>47.26400150798319</v>
+        <v>61.74696784082273</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16.31567192982902</v>
+        <v>15.35610190823388</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.958185921330617</v>
+        <v>2.564407789822586</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.914447824151116</v>
+        <v>0.976940995894704</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6263</v>
+        <v>6435</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>559.1726266424835</v>
+        <v>565.3622245638517</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>165.5</v>
+        <v>260</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.55245333029796</v>
+        <v>47.26400150798319</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12.75215822364444</v>
+        <v>16.31567192982902</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6794076078918447</v>
+        <v>1.958185921330617</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6400325968088065</v>
+        <v>2.914447824151116</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6279</v>
+        <v>6263</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>558.2339961290573</v>
+        <v>559.1726266424835</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>127</v>
+        <v>165.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.36330552587825</v>
+        <v>59.55245333029796</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15.99076948518842</v>
+        <v>12.75215822364444</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6218522680812315</v>
+        <v>0.6794076078918447</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.2363843412215835</v>
+        <v>0.6400325968088065</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6237</v>
+        <v>6279</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>553.1624981558506</v>
+        <v>558.2339961290573</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>35.2</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.99360438501209</v>
+        <v>57.36330552587825</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.44276380005408</v>
+        <v>15.99076948518842</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.097505839344393</v>
+        <v>0.6218522680812315</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.4507018063713963</v>
+        <v>-0.2363843412215835</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6175</v>
+        <v>6237</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>550.9029365627376</v>
+        <v>553.1624981558506</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>76.8</v>
+        <v>35.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46.5339987911337</v>
+        <v>50.99360438501209</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19.13504901359752</v>
+        <v>22.44276380005408</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.904619479937037</v>
+        <v>1.097505839344393</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.8118251722129326</v>
+        <v>0.4507018063713963</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6446</v>
+        <v>6175</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>535.8010776393595</v>
+        <v>550.9029365627376</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1545</v>
+        <v>76.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.19129235367168</v>
+        <v>46.5339987911337</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>36.97204546865093</v>
+        <v>19.13504901359752</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.023326416480007</v>
+        <v>1.904619479937037</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>12.65351345053263</v>
+        <v>0.8118251722129326</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6472</v>
+        <v>6446</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>520.9712675240604</v>
+        <v>535.8010776393595</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>435</v>
+        <v>1545</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.23162666339669</v>
+        <v>64.19129235367168</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.01872851240987</v>
+        <v>36.97204546865093</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6774247421735233</v>
+        <v>1.023326416480007</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.153630574639546</v>
+        <v>12.65351345053263</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6173</v>
+        <v>6472</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>515.6244352996924</v>
+        <v>520.9712675240604</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>239</v>
+        <v>435</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.62088414880052</v>
+        <v>53.23162666339669</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.4490954828624</v>
+        <v>30.01872851240987</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.236559362589119</v>
+        <v>0.6774247421735233</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>5.288093809646383</v>
+        <v>2.153630574639546</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6419</v>
+        <v>6173</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>511.7346347621678</v>
+        <v>515.6244352996924</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>154</v>
+        <v>239</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.10969393183165</v>
+        <v>60.62088414880052</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.96352159268069</v>
+        <v>18.4490954828624</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5543557108942232</v>
+        <v>1.236559362589119</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.003678473111092</v>
+        <v>5.288093809646383</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6170</v>
+        <v>6419</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>510.9737452021472</v>
+        <v>511.7346347621678</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>48.7</v>
+        <v>154</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.87316342198224</v>
+        <v>52.10969393183165</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.62973438293024</v>
+        <v>22.96352159268069</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.328419899795577</v>
+        <v>0.5543557108942232</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3071501608575315</v>
+        <v>-1.003678473111092</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6416</v>
+        <v>6170</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>507.2306052356462</v>
+        <v>510.9737452021472</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>100.5</v>
+        <v>48.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.68491343423481</v>
+        <v>59.87316342198224</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.18679627488019</v>
+        <v>22.62973438293024</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7120825074308554</v>
+        <v>1.328419899795577</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0370771972821259</v>
+        <v>0.3071501608575315</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6174</v>
+        <v>6416</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>502.0400247298541</v>
+        <v>507.2306052356462</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45.55</v>
+        <v>100.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.25242209637744</v>
+        <v>54.68491343423481</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13.14254361812471</v>
+        <v>15.18679627488019</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4193879097243387</v>
+        <v>0.7120825074308554</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5021054851771137</v>
+        <v>0.0370771972821259</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6291</v>
+        <v>6174</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>494.7742902676001</v>
+        <v>502.0400247298541</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>400.5</v>
+        <v>45.55</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.85003065508189</v>
+        <v>51.25242209637744</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.63492481856979</v>
+        <v>13.14254361812471</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.072095663081945</v>
+        <v>0.4193879097243387</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>7.287706320092807</v>
+        <v>0.5021054851771137</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6259</v>
+        <v>6291</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>477.4396460159516</v>
+        <v>494.7742902676001</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>31.75</v>
+        <v>400.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.56306860794313</v>
+        <v>51.85003065508189</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.62582170750973</v>
+        <v>16.63492481856979</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.446261807903215</v>
+        <v>2.072095663081945</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1446846854098987</v>
+        <v>7.287706320092807</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6207</v>
+        <v>6259</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>475.2675656740154</v>
+        <v>477.4396460159516</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>111</v>
+        <v>31.75</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.94776785096845</v>
+        <v>52.56306860794313</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>14.0112972316025</v>
+        <v>10.62582170750973</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.559500269989604</v>
+        <v>1.446261807903215</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.677214377350343</v>
+        <v>0.1446846854098987</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6423</v>
+        <v>6207</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>474.3245576878028</v>
+        <v>475.2675656740154</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>111</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.58319715958275</v>
+        <v>51.94776785096845</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.88745882328509</v>
+        <v>14.0112972316025</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4078120710478514</v>
+        <v>1.559500269989604</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3414882727416246</v>
+        <v>1.677214377350343</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6204</v>
+        <v>6423</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>462.1224552186068</v>
+        <v>474.3245576878028</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>57.02079273045774</v>
+        <v>56.58319715958275</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18.43084671172283</v>
+        <v>15.88745882328509</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.044500897357133</v>
+        <v>0.4078120710478514</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.44224527028846</v>
+        <v>0.3414882727416246</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6449</v>
+        <v>6204</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>460.6618748371263</v>
+        <v>462.1224552186068</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>237</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.38887030804914</v>
+        <v>57.02079273045774</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.58315881884735</v>
+        <v>18.43084671172283</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.511025486023218</v>
+        <v>3.044500897357133</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3.689088689701862</v>
+        <v>1.44224527028846</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6185</v>
+        <v>6449</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>434.6997843927652</v>
+        <v>460.6618748371263</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.65</v>
+        <v>237</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>29.77127464225732</v>
+        <v>49.38887030804914</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25.64379000446028</v>
+        <v>24.58315881884735</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6182511143073882</v>
+        <v>3.511025486023218</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0662192697496226</v>
+        <v>3.689088689701862</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6210</v>
+        <v>6185</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>430.4953875249219</v>
+        <v>434.6997843927652</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18.05</v>
+        <v>12.65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.5932367200336</v>
+        <v>29.77127464225732</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6.725795539635822</v>
+        <v>25.64379000446028</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.1085244745973179</v>
+        <v>0.6182511143073882</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1379442792191344</v>
+        <v>-0.0662192697496226</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>428.9261518403976</v>
+        <v>430.4953875249219</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>25.9</v>
+        <v>18.05</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.47451663847761</v>
+        <v>51.5932367200336</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.38136071901567</v>
+        <v>6.725795539635822</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.184980529164982</v>
+        <v>0.1085244745973179</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3039984578961547</v>
+        <v>0.1379442792191344</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6415</v>
+        <v>6220</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>427.6799074905534</v>
+        <v>428.9261518403976</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>458</v>
+        <v>25.9</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.15178573589615</v>
+        <v>42.47451663847761</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11.31310597754299</v>
+        <v>22.38136071901567</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.378073766106229</v>
+        <v>1.184980529164982</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>4.752995185122723</v>
+        <v>0.3039984578961547</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6208</v>
+        <v>6415</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>424.4245981761354</v>
+        <v>427.6799074905534</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>82.7</v>
+        <v>458</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.16256896810333</v>
+        <v>49.15178573589615</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9.036185608400103</v>
+        <v>11.31310597754299</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6379396716921866</v>
+        <v>1.378073766106229</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.4009681186222096</v>
+        <v>4.752995185122723</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6464</v>
+        <v>6208</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>421.1628433975877</v>
+        <v>424.4245981761354</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.23754751029882</v>
+        <v>49.16256896810333</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.3614898747337</v>
+        <v>9.036185608400103</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.0264456456029753</v>
+        <v>0.6379396716921866</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0482342125525407</v>
+        <v>0.4009681186222096</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>420.5907742526043</v>
+        <v>421.1628433975877</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>101</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.89135720946131</v>
+        <v>43.23754751029882</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12.23656176637316</v>
+        <v>30.3614898747337</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.209885155478894</v>
+        <v>0.0264456456029753</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.6630354197146278</v>
+        <v>-0.0482342125525407</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6474</v>
+        <v>6462</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>417.4166039771195</v>
+        <v>420.5907742526043</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>37.2</v>
+        <v>101</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.94906914469832</v>
+        <v>50.89135720946131</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.52416864362302</v>
+        <v>12.23656176637316</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.34166039771195</v>
+        <v>1.209885155478894</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1306484979613549</v>
+        <v>0.6630354197146278</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6241</v>
+        <v>6474</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>414.5609851099871</v>
+        <v>417.4166039771195</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>17.95</v>
+        <v>37.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>64.24087223278788</v>
+        <v>42.94906914469832</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.75233044816658</v>
+        <v>14.52416864362302</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5703510131950319</v>
+        <v>1.34166039771195</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2491523504345987</v>
+        <v>-0.1306484979613549</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6274</v>
+        <v>6241</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>412.270691863583</v>
+        <v>414.5609851099871</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1490</v>
+        <v>17.95</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.12197071468819</v>
+        <v>64.24087223278788</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.92753830817594</v>
+        <v>23.75233044816658</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9268584740680228</v>
+        <v>0.5703510131950319</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-6.403204721060959</v>
+        <v>0.2491523504345987</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6234</v>
+        <v>6274</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>409.4035175615221</v>
+        <v>412.270691863583</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>36.8</v>
+        <v>1490</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.97575090432648</v>
+        <v>51.12197071468819</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.28136961737346</v>
+        <v>12.92753830817594</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.064029708868585</v>
+        <v>0.9268584740680228</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.4117766085772416</v>
+        <v>-6.403204721060959</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6163</v>
+        <v>6234</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>393.8380620056482</v>
+        <v>409.4035175615221</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>43.3</v>
+        <v>36.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.83257002002662</v>
+        <v>50.97575090432648</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.58435840139506</v>
+        <v>19.28136961737346</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3501319006439303</v>
+        <v>1.064029708868585</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2866547032570856</v>
+        <v>0.4117766085772416</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6227</v>
+        <v>6163</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>391.9745330145391</v>
+        <v>393.8380620056482</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>113</v>
+        <v>43.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.62766745040317</v>
+        <v>51.83257002002662</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10.53080062410892</v>
+        <v>16.58435840139506</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.054870709294181</v>
+        <v>0.3501319006439303</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.6635121858485432</v>
+        <v>0.2866547032570856</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6442</v>
+        <v>6227</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>384.5979482790846</v>
+        <v>391.9745330145391</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1615</v>
+        <v>113</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.24637714399277</v>
+        <v>42.62766745040317</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.95431833788605</v>
+        <v>10.53080062410892</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.493409533669333</v>
+        <v>4.054870709294181</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>17.52843645163279</v>
+        <v>-0.6635121858485432</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6229</v>
+        <v>6442</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>383.3000374553882</v>
+        <v>384.5979482790846</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.1</v>
+        <v>1615</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.34524013146724</v>
+        <v>57.24637714399277</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13.68205950377573</v>
+        <v>19.95431833788605</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.762612414550255</v>
+        <v>0.493409533669333</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0991587690144452</v>
+        <v>17.52843645163279</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6412</v>
+        <v>6229</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>376.360288894505</v>
+        <v>383.3000374553882</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.21767055504127</v>
+        <v>52.34524013146724</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.10644298527706</v>
+        <v>13.68205950377573</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7415293581518918</v>
+        <v>1.762612414550255</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.443540842323328</v>
+        <v>0.0991587690144452</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6184</v>
+        <v>6412</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>371.1568356212218</v>
+        <v>376.360288894505</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>41.15</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>21.62858491618736</v>
+        <v>47.21767055504127</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.10473848119856</v>
+        <v>25.10644298527706</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.018218801074867</v>
+        <v>0.7415293581518918</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.006847004746841</v>
+        <v>0.443540842323328</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6270</v>
+        <v>6184</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>367.8605009579209</v>
+        <v>371.1568356212218</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>29.95</v>
+        <v>41.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.40322508293248</v>
+        <v>21.62858491618736</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>9.46827354533465</v>
+        <v>24.10473848119856</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7889084630381776</v>
+        <v>2.018218801074867</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.132156110709524</v>
+        <v>-0.006847004746841</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6244</v>
+        <v>6270</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>366.0008243905912</v>
+        <v>367.8605009579209</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>24.4</v>
+        <v>29.95</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.43175601889502</v>
+        <v>47.40322508293248</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16.7927897377716</v>
+        <v>9.46827354533465</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8132732249174556</v>
+        <v>0.7889084630381776</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0455341167057048</v>
+        <v>0.132156110709524</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6409</v>
+        <v>6244</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>359.4423663389936</v>
+        <v>366.0008243905912</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1030</v>
+        <v>24.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.00282509475455</v>
+        <v>47.43175601889502</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.82458603953884</v>
+        <v>16.7927897377716</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9133591150753484</v>
+        <v>0.8132732249174556</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.908216477448301</v>
+        <v>0.0455341167057048</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6470</v>
+        <v>6409</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>359.4104136311823</v>
+        <v>359.4423663389936</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>41.5</v>
+        <v>1030</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>30.03800412225367</v>
+        <v>53.00282509475455</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>44.49327720108618</v>
+        <v>19.82458603953884</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.838312980571893</v>
+        <v>0.9133591150753484</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1677168333790377</v>
+        <v>2.908216477448301</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6275</v>
+        <v>6470</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>355.5467219852067</v>
+        <v>359.4104136311823</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>45.7</v>
+        <v>41.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.84932866837448</v>
+        <v>30.03800412225367</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.7208457549255</v>
+        <v>44.49327720108618</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9285922868864732</v>
+        <v>1.838312980571893</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3662160488750076</v>
+        <v>0.1677168333790377</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6441</v>
+        <v>6275</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>354.7319013947222</v>
+        <v>355.5467219852067</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>21.25</v>
+        <v>45.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.35393956337096</v>
+        <v>54.84932866837448</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.79559484497857</v>
+        <v>20.7208457549255</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2287842697406492</v>
+        <v>0.9285922868864732</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0455670878242028</v>
+        <v>0.3662160488750076</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6223</v>
+        <v>6441</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>352.0178342813626</v>
+        <v>354.7319013947222</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>5030</v>
+        <v>21.25</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>38.99996869182381</v>
+        <v>46.35393956337096</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.49696131085538</v>
+        <v>20.79559484497857</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.720442525144879</v>
+        <v>0.2287842697406492</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-87.89762703964971</v>
+        <v>-0.0455670878242028</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6177</v>
+        <v>6223</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>348.0789735296511</v>
+        <v>352.0178342813626</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>47.55</v>
+        <v>5030</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.98412584385693</v>
+        <v>38.99996869182381</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.30949566943033</v>
+        <v>17.49696131085538</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5017343842174131</v>
+        <v>1.720442525144879</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0896014490521822</v>
+        <v>-87.89762703964971</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6477</v>
+        <v>6177</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>347.1079109224706</v>
+        <v>348.0789735296511</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>37.05</v>
+        <v>47.55</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.52182334116729</v>
+        <v>48.98412584385693</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.29824582664845</v>
+        <v>22.30949566943033</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.93870330744171</v>
+        <v>0.5017343842174131</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0820561911325131</v>
+        <v>-0.0896014490521822</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6261</v>
+        <v>6477</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>346.6161974133568</v>
+        <v>347.1079109224706</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>79</v>
+        <v>37.05</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.61462627794441</v>
+        <v>51.52182334116729</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.11080892504607</v>
+        <v>19.29824582664845</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.599697291418178</v>
+        <v>0.93870330744171</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.8251722097627407</v>
+        <v>0.0820561911325131</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6285</v>
+        <v>6261</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>342.1137505009763</v>
+        <v>346.6161974133568</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.5117609128559</v>
+        <v>46.61462627794441</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.65286880017313</v>
+        <v>24.11080892504607</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8739918625535201</v>
+        <v>0.599697291418178</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.9593927139235769</v>
+        <v>0.8251722097627407</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6182</v>
+        <v>6285</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>338.6366182498644</v>
+        <v>342.1137505009763</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.13765272743972</v>
+        <v>52.5117609128559</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.81016665108128</v>
+        <v>14.65286880017313</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.213413776033681</v>
+        <v>0.8739918625535201</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.9265515078521238</v>
+        <v>0.9593927139235769</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6405</v>
+        <v>6182</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.3338712222049</v>
+        <v>338.6366182498644</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>40.25</v>
+        <v>110</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.72265707437822</v>
+        <v>49.13765272743972</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.54390258398169</v>
+        <v>12.81016665108128</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7389387444466331</v>
+        <v>1.213413776033681</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.8259068597699337</v>
+        <v>0.9265515078521238</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6432</v>
+        <v>6405</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>323.5462144049748</v>
+        <v>333.3338712222049</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>40.25</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.45570214660007</v>
+        <v>46.72265707437822</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.19116676537168</v>
+        <v>24.54390258398169</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6213561482179417</v>
+        <v>0.7389387444466331</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.7211590378078467</v>
+        <v>0.8259068597699337</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6194</v>
+        <v>6432</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>322.5908232948232</v>
+        <v>323.5462144049748</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>29.75</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45.21827202448242</v>
+        <v>43.45570214660007</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.30738593648126</v>
+        <v>13.19116676537168</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1230707791896783</v>
+        <v>0.6213561482179417</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0918261252179387</v>
+        <v>-0.7211590378078467</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6217</v>
+        <v>6194</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>314.5316449997685</v>
+        <v>322.5908232948232</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>175</v>
+        <v>29.75</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.40506400943818</v>
+        <v>45.21827202448242</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.31692475889225</v>
+        <v>23.30738593648126</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4.33486317435983</v>
+        <v>0.1230707791896783</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>5.036421131024584</v>
+        <v>0.0918261252179387</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6167</v>
+        <v>6217</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>307.3855596769686</v>
+        <v>314.5316449997685</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10.8</v>
+        <v>175</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.93181629537075</v>
+        <v>54.40506400943818</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.24282284221066</v>
+        <v>14.31692475889225</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.90282628172046</v>
+        <v>4.33486317435983</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0809255956632683</v>
+        <v>5.036421131024584</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6411</v>
+        <v>6167</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>303.5091746935789</v>
+        <v>307.3855596769686</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.09104576974312</v>
+        <v>51.93181629537075</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.83096258585797</v>
+        <v>14.24282284221066</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8576720603347204</v>
+        <v>1.90282628172046</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.7924503329776313</v>
+        <v>0.0809255956632683</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6266</v>
+        <v>6411</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>300.6321083486163</v>
+        <v>303.5091746935789</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>25</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.37700214538894</v>
+        <v>50.09104576974312</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.33527041754093</v>
+        <v>14.83096258585797</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.013325201321883</v>
+        <v>0.8576720603347204</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0514124334544068</v>
+        <v>0.7924503329776313</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6233</v>
+        <v>6266</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>297.0458991394158</v>
+        <v>300.6321083486163</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.97364237328794</v>
+        <v>49.37700214538894</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.08153097060021</v>
+        <v>11.33527041754093</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7111792673913935</v>
+        <v>1.013325201321883</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1731308787126361</v>
+        <v>0.0514124334544068</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6198</v>
+        <v>6233</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>288.4497852454349</v>
+        <v>297.0458991394158</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>19.4</v>
+        <v>21.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.37019903168825</v>
+        <v>50.97364237328794</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5.795319858454928</v>
+        <v>15.08153097060021</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2859652996995775</v>
+        <v>0.7111792673913935</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.162056472757117</v>
+        <v>0.1731308787126361</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6236</v>
+        <v>6198</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>283.6617050652613</v>
+        <v>288.4497852454349</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.2661279169273</v>
+        <v>51.37019903168825</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.976568976137196</v>
+        <v>5.795319858454928</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v>0.2859652996995775</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2234751754226422</v>
+        <v>0.162056472757117</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6451</v>
+        <v>6236</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>279.794120283499</v>
+        <v>283.6617050652613</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>453.5</v>
+        <v>0</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.91579407596211</v>
+        <v>47.2661279169273</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.69752315441651</v>
+        <v>9.976568976137196</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.234114533486751</v>
+        <v>0</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,51 +4227,51 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>6.255058280117531</v>
+        <v>0.2234751754226422</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6288</v>
+        <v>6451</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>274.1623227954031</v>
+        <v>279.794120283499</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.95</v>
+        <v>453.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G72" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.12010230369736</v>
+        <v>52.91579407596211</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v/>
+        <v>10.69752315441651</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>1.234114533486751</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,51 +4280,51 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0137243745044277</v>
+        <v>6.255058280117531</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6414</v>
+        <v>6288</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>264.0002721951551</v>
+        <v>274.1623227954031</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>390</v>
+        <v>20.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.68839979028543</v>
+        <v>45.12010230369736</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.4106716409476</v>
+        <v/>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4560360981553977</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-5.616624631806086</v>
+        <v>0.0137243745044277</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6417</v>
+        <v>6414</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>263.0502509771013</v>
+        <v>264.0002721951551</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>106</v>
+        <v>390</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.25788448581032</v>
+        <v>41.68839979028543</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.06731680536659</v>
+        <v>18.4106716409476</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4860053056529334</v>
+        <v>0.4560360981553977</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1162007515605383</v>
+        <v>-5.616624631806086</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6283</v>
+        <v>6417</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>258.9769870105815</v>
+        <v>263.0502509771013</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.04361467917883</v>
+        <v>36.25788448581032</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>30.73239472754121</v>
+        <v>25.06731680536659</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7993180288706967</v>
+        <v>0.4860053056529334</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0971779482326786</v>
+        <v>0.1162007515605383</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6245</v>
+        <v>6283</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>254.5299629977683</v>
+        <v>258.9769870105815</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>83.2</v>
+        <v>20</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.64279509996974</v>
+        <v>41.04361467917883</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.27973762696614</v>
+        <v>30.73239472754121</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8440487803055989</v>
+        <v>0.7993180288706967</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1500699578030893</v>
+        <v>0.0971779482326786</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6276</v>
+        <v>6245</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>250.6624404691856</v>
+        <v>254.5299629977683</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>20.25</v>
+        <v>83.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.01658479242569</v>
+        <v>51.64279509996974</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.49175526444076</v>
+        <v>11.27973762696614</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.122719002771823</v>
+        <v>0.8440487803055989</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2275014374274705</v>
+        <v>-0.1500699578030893</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6246</v>
+        <v>6276</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>249.6520045124877</v>
+        <v>250.6624404691856</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>12.25</v>
+        <v>20.25</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.68750515171868</v>
+        <v>50.01658479242569</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.73803786984623</v>
+        <v>22.49175526444076</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2983311302048909</v>
+        <v>1.122719002771823</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.087105725225745</v>
+        <v>0.2275014374274705</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6443</v>
+        <v>6246</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>231.263796666794</v>
+        <v>249.6520045124877</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>26.65</v>
+        <v>12.25</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.86875087372697</v>
+        <v>41.68750515171868</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.22248963298686</v>
+        <v>20.73803786984623</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.222973149677565</v>
+        <v>0.2983311302048909</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2854786076686182</v>
+        <v>0.087105725225745</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6222</v>
+        <v>6443</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>209.2952005868291</v>
+        <v>231.263796666794</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>20.05</v>
+        <v>26.65</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.33754290463593</v>
+        <v>45.86875087372697</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.04375991103098</v>
+        <v>13.22248963298686</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3632252586844889</v>
+        <v>1.222973149677565</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.3958481005208724</v>
+        <v>0.2854786076686182</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6228</v>
+        <v>6222</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>167.3930883486433</v>
+        <v>209.2952005868291</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.24634457150348</v>
+        <v>51.33754290463593</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.793237500110434</v>
+        <v>9.04375991103098</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.0115692307692307</v>
+        <v>0.3632252586844889</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.5313049805255357</v>
+        <v>0.3958481005208724</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6188</v>
+        <v>6228</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>110.3490826174812</v>
+        <v>167.3930883486433</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.93803173043239</v>
+        <v>39.24634457150348</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.60514702148712</v>
+        <v>7.793237500110434</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6140222457569217</v>
+        <v>0.0115692307692307</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1391087176259233</v>
+        <v>-0.5313049805255357</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,52 +4820,105 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
+        <v>6188</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>廣明</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>110.3490826174812</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>43.93803173043239</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>18.60514702148712</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.6140222457569217</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.1391087176259233</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
         <v>79.69256883947179</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E84" s="2" t="n">
         <v>59.6</v>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
         <v>30.58572186742816</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>17.3651698807019</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J84" s="2" t="n">
         <v>0.5193246202755211</v>
       </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
         <v>0.1237877631542381</v>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq6_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6190</v>
+        <v>6269</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>908.0422813305056</v>
+        <v>1076.866360161651</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.54478689459793</v>
+        <v>69.0565935561639</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>24.16846813240486</v>
+        <v>18.95293576211244</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.092083637897586</v>
+        <v>3.317569652842301</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>4</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.8248628755630365</v>
+        <v>1.126750332551275</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6218</v>
+        <v>6190</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>761.990328263318</v>
+        <v>1048.042281330506</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.41814208357266</v>
+        <v>55.54478688344963</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.509466091206</v>
+        <v>24.16846821071943</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.499032826331798</v>
+        <v>2.092083637897586</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4684142821494099</v>
+        <v>0.8248628755057901</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6465</v>
+        <v>6272</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>757.7729676303591</v>
+        <v>988.6568317384912</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>48.4</v>
+        <v>26.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>50.54275647676374</v>
+        <v>59.81443589785707</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.16588414638556</v>
+        <v>41.15198242645968</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.541141419597373</v>
+        <v>2.224308148953574</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>3</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4848487660302825</v>
+        <v>0.4330522603451958</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6418</v>
+        <v>6257</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>684</v>
+        <v>956.9911938620965</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37.85</v>
+        <v>219</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>71.09172994680721</v>
+        <v>58.84513757438231</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.69407808855428</v>
+        <v>13.5571818080963</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.936845848249604</v>
+        <v>2.515268478844681</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5718159089985602</v>
+        <v>1.967058107940569</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6292</v>
+        <v>6187</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>665.3765981082721</v>
+        <v>955.0988982385276</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>62.9</v>
+        <v>1365</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.12886558444075</v>
+        <v>60.10527808559113</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.20249855472768</v>
+        <v>22.43893496974433</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5251641018441701</v>
+        <v>1.528597430477842</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1392540119858683</v>
+        <v>14.10142638932409</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6187</v>
+        <v>6438</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>660.0988982385247</v>
+        <v>953.6067864313402</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1365</v>
+        <v>151</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.10527807911073</v>
+        <v>57.19483038705259</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.43893490479889</v>
+        <v>14.25111749638185</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.528597430477842</v>
+        <v>2.327848704847906</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>14.10142639037338</v>
+        <v>0.9605244107124582</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6225</v>
+        <v>6456</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>657.4762881015786</v>
+        <v>935.542626497388</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>59.5</v>
+        <v>74.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.42976435018691</v>
+        <v>61.74696784330017</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>51.8201513849315</v>
+        <v>15.356101979078</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.078394137815737</v>
+        <v>2.564407789822586</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>4</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.884597247182206</v>
+        <v>0.9769409957802349</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6438</v>
+        <v>6218</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>618.6067864313409</v>
+        <v>931.990328263318</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>151</v>
+        <v>40.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.19483006345361</v>
+        <v>66.41814209672221</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.25111738375986</v>
+        <v>31.50946609444125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.327848704847906</v>
+        <v>2.499032826331798</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.9605244132881998</v>
+        <v>0.4684142821398722</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6284</v>
+        <v>6226</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>608.0648281424041</v>
+        <v>927.2469799796052</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>53.14340517031061</v>
+        <v>77.91259859767868</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.02257106718804</v>
+        <v>26.76378837511832</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.897662852765586</v>
+        <v>0.3246979979605265</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.005026002669722</v>
+        <v>1.311437906675956</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6290</v>
+        <v>6465</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>605.9113494879764</v>
+        <v>897.7729676303591</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>248</v>
+        <v>48.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.82341983742649</v>
+        <v>50.54275616044588</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.26214737873338</v>
+        <v>15.1658840241981</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.191134948797634</v>
+        <v>1.541141419597373</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>6.567802564555347</v>
+        <v>0.484848766569808</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6426</v>
+        <v>6418</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>594.8068496958571</v>
+        <v>884</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>263.5</v>
+        <v>37.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>67.11578250326315</v>
+        <v>71.09172994680721</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32.47468482274172</v>
+        <v>25.69407810844764</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.125632550007205</v>
+        <v>7.936845848249604</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4.055744527284368</v>
+        <v>0.5718159090176373</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6265</v>
+        <v>6426</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>579.9118456708223</v>
+        <v>864.8068496958571</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>57.1</v>
+        <v>263.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>52.78109223899119</v>
+        <v>67.11578251300506</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.97010456817325</v>
+        <v>32.4746849340702</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4528480115497993</v>
+        <v>1.125632550007205</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.18951666906253</v>
+        <v>4.055744527036357</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6456</v>
+        <v>6290</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>570.542626497388</v>
+        <v>805.9113494879764</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>74.3</v>
+        <v>248</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.74696784082273</v>
+        <v>57.82341983383978</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15.35610190823388</v>
+        <v>25.26214735915178</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.564407789822586</v>
+        <v>1.191134948797634</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.976940995894704</v>
+        <v>6.567802564574432</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6435</v>
+        <v>6213</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>565.3622245638517</v>
+        <v>801.376344447271</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>260</v>
+        <v>582</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>47.26400150798319</v>
+        <v>74.0303206125861</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>16.31567192982902</v>
+        <v>30.48695830496024</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.958185921330617</v>
+        <v>1.365317242601434</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.914447824151116</v>
+        <v>10.03494381781199</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6263</v>
+        <v>6446</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>559.1726266424835</v>
+        <v>780.8010776393595</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>165.5</v>
+        <v>1545</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.55245333029796</v>
+        <v>64.19129236324804</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.75215822364444</v>
+        <v>36.97204551483281</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6794076078918447</v>
+        <v>1.023326416480007</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.6400325968088065</v>
+        <v>12.65351344824306</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>558.2339961290573</v>
+        <v>748.0648281424041</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>127</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.36330552587825</v>
+        <v>53.14340516145359</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.99076948518842</v>
+        <v>17.02257107049128</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6218522680812315</v>
+        <v>2.897662852765586</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.2363843412215835</v>
+        <v>1.005026002440756</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6237</v>
+        <v>6271</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>553.1624981558506</v>
+        <v>736.244747528148</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35.2</v>
+        <v>215</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.99360438501209</v>
+        <v>60.56269871748957</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.44276380005408</v>
+        <v>13.96506041430599</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.097505839344393</v>
+        <v>1.395885047223786</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4507018063713963</v>
+        <v>3.795161760695593</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6175</v>
+        <v>6173</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>550.9029365627376</v>
+        <v>715.6244352996924</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>76.8</v>
+        <v>239</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46.5339987911337</v>
+        <v>60.62088415307932</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.13504901359752</v>
+        <v>18.44909553007616</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.904619479937037</v>
+        <v>1.236559362589119</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.8118251722129326</v>
+        <v>5.288093809560524</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6446</v>
+        <v>6214</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>535.8010776393595</v>
+        <v>698.83562321383</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1545</v>
+        <v>181</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.19129235367168</v>
+        <v>73.85084465290811</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>36.97204546865093</v>
+        <v>35.38709895146452</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.023326416480007</v>
+        <v>0.3260443554702251</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>12.65351345053263</v>
+        <v>1.150987415675576</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6472</v>
+        <v>6435</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>520.9712675240604</v>
+        <v>680.3622245638517</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>435</v>
+        <v>260</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.23162666339669</v>
+        <v>47.26400150452629</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.01872851240987</v>
+        <v>16.31567187939121</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6774247421735233</v>
+        <v>1.958185921330617</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.153630574639546</v>
+        <v>2.914447824246533</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6173</v>
+        <v>6202</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>515.6244352996924</v>
+        <v>671.6525872798718</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>239</v>
+        <v>59.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.62088414880052</v>
+        <v>51.25399308112272</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.4490954828624</v>
+        <v>13.27085657543991</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.236559362589119</v>
+        <v>0.4739353636810326</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.288093809646383</v>
+        <v>0.0942754535647953</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6419</v>
+        <v>6209</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>511.7346347621678</v>
+        <v>670.1248601240783</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>154</v>
+        <v>76.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.10969393183165</v>
+        <v>58.01541107061195</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.96352159268069</v>
+        <v>12.98596148351179</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5543557108942232</v>
+        <v>1.820350518083856</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.003678473111092</v>
+        <v>0.9963844444379636</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6170</v>
+        <v>6237</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>510.9737452021472</v>
+        <v>668.1624981558506</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>48.7</v>
+        <v>35.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>59.87316342198224</v>
+        <v>50.99360444406045</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.62973438293024</v>
+        <v>22.44276391577818</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.328419899795577</v>
+        <v>1.097505839344393</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3071501608575315</v>
+        <v>0.4507018061996859</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6416</v>
+        <v>6175</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>507.2306052356462</v>
+        <v>665.9029365627375</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>100.5</v>
+        <v>76.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.68491343423481</v>
+        <v>46.53399879878815</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.18679627488019</v>
+        <v>19.13504909060159</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7120825074308554</v>
+        <v>1.904619479937037</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0370771972821259</v>
+        <v>0.8118251721175369</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6174</v>
+        <v>6292</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>502.0400247298541</v>
+        <v>665.3765981082721</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45.55</v>
+        <v>62.9</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.25242209637744</v>
+        <v>58.1288655711463</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.14254361812471</v>
+        <v>26.20249854350446</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4193879097243387</v>
+        <v>0.5251641018441701</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.5021054851771137</v>
+        <v>-0.1392540120431056</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6291</v>
+        <v>6225</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>494.7742902676001</v>
+        <v>657.4762881015786</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>400.5</v>
+        <v>59.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.85003065508189</v>
+        <v>67.42976435018691</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.63492481856979</v>
+        <v>51.8201513849315</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.072095663081945</v>
+        <v>1.078394137815737</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>7.287706320092807</v>
+        <v>1.884597247182206</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6259</v>
+        <v>6278</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>477.4396460159516</v>
+        <v>657.1650094928373</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>31.75</v>
+        <v>201.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.56306860794313</v>
+        <v>63.5396318305331</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10.62582170750973</v>
+        <v>20.02999254412236</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.446261807903215</v>
+        <v>1.01650094928373</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1446846854098987</v>
+        <v>4.600557605471255</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6207</v>
+        <v>6170</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>475.2675656740154</v>
+        <v>625.9737452021471</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>111</v>
+        <v>48.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.94776785096845</v>
+        <v>59.87316342198224</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.0112972316025</v>
+        <v>22.62973439205703</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.559500269989604</v>
+        <v>1.328419899795577</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.677214377350343</v>
+        <v>0.3071501607048953</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6423</v>
+        <v>6168</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>474.3245576878028</v>
+        <v>617.6722671275644</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>28.85</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.58319715958275</v>
+        <v>63.80975361035744</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.88745882328509</v>
+        <v>18.17287022846343</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4078120710478514</v>
+        <v>1.328067842870905</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.3414882727416246</v>
+        <v>0.6463097873018474</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6204</v>
+        <v>6259</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>462.1224552186068</v>
+        <v>617.4396460159516</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>31.75</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.02079273045774</v>
+        <v>52.56306862733273</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.43084671172283</v>
+        <v>10.62582182131096</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.044500897357133</v>
+        <v>1.446261807903215</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,11 +2107,11 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.44224527028846</v>
+        <v>0.144684685343119</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>460.6618748371263</v>
+        <v>615.6618748371262</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>237</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.38887030804914</v>
+        <v>49.38887031981305</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.58315881884735</v>
+        <v>24.5831588829992</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>3.511025486023218</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>3.689088689701862</v>
+        <v>3.6890886889387</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6185</v>
+        <v>6207</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>434.6997843927652</v>
+        <v>615.2675656740154</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12.65</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>29.77127464225732</v>
+        <v>51.94776787526314</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.64379000446028</v>
+        <v>14.01129741169568</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6182511143073882</v>
+        <v>1.559500269989604</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0662192697496226</v>
+        <v>1.677214376901978</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6210</v>
+        <v>6241</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>430.4953875249219</v>
+        <v>614.5609851099871</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.05</v>
+        <v>17.95</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.5932367200336</v>
+        <v>64.24087214910422</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6.725795539635822</v>
+        <v>23.7523304353861</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1085244745973179</v>
+        <v>0.5703510131950319</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1379442792191344</v>
+        <v>0.249152350476651</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6220</v>
+        <v>6291</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>428.9261518403976</v>
+        <v>609.7742902676002</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>25.9</v>
+        <v>400.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>42.47451663847761</v>
+        <v>51.85003065475721</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.38136071901567</v>
+        <v>16.63492485222364</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.184980529164982</v>
+        <v>2.072095663081945</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3039984578961547</v>
+        <v>7.287706320073738</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6415</v>
+        <v>6224</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>427.6799074905534</v>
+        <v>604.9425870255443</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>458</v>
+        <v>74.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.15178573589615</v>
+        <v>61.27352925925855</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.31310597754299</v>
+        <v>32.46182261968857</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.378073766106229</v>
+        <v>1.215680902140303</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4.752995185122723</v>
+        <v>1.822001008691069</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6208</v>
+        <v>6415</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>424.4245981761354</v>
+        <v>603.9632117455222</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>82.7</v>
+        <v>458</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.16256896810333</v>
+        <v>49.15178576054042</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.036185608400103</v>
+        <v>11.31310594661383</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6379396716921866</v>
+        <v>1.560561866695306</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4009681186222096</v>
+        <v>4.752995183310214</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6464</v>
+        <v>6205</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>421.1628433975877</v>
+        <v>590.8628781288422</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.23754751029882</v>
+        <v>57.16615281564503</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.3614898747337</v>
+        <v>16.92090470804848</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.0264456456029753</v>
+        <v>1.65148187363647</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0482342125525407</v>
+        <v>0.9777260409975768</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6462</v>
+        <v>6197</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>420.5907742526043</v>
+        <v>588.4816384323698</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>101</v>
+        <v>309.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.89135720946131</v>
+        <v>52.29989694687208</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12.23656176637316</v>
+        <v>16.31739474612889</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.209885155478894</v>
+        <v>0.8571206728128303</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.6630354197146278</v>
+        <v>1.796634398406524</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6474</v>
+        <v>6265</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>417.4166039771195</v>
+        <v>579.9118456708223</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>37.2</v>
+        <v>57.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.94906914469832</v>
+        <v>52.78109223926123</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.52416864362302</v>
+        <v>22.97010462362652</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.34166039771195</v>
+        <v>0.4528480115497993</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1306484979613549</v>
+        <v>-0.1895166690777934</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6241</v>
+        <v>6164</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>414.5609851099871</v>
+        <v>564.0334519829106</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>17.95</v>
+        <v>12.35</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.24087223278788</v>
+        <v>52.98449916373372</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.75233044816658</v>
+        <v>21.41641820361393</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5703510131950319</v>
+        <v>1.219046322617536</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2491523504345987</v>
+        <v>0.127387258566285</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6274</v>
+        <v>6263</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>412.270691863583</v>
+        <v>559.1726266424835</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1490</v>
+        <v>165.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.12197071468819</v>
+        <v>59.55245341580157</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12.92753830817594</v>
+        <v>12.7521582608838</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9268584740680228</v>
+        <v>0.6794076078918447</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-6.403204721060959</v>
+        <v>0.6400325962364384</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6234</v>
+        <v>6183</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>409.4035175615221</v>
+        <v>558.3788466257623</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>36.8</v>
+        <v>91</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>50.97575090432648</v>
+        <v>41.49795956351056</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.28136961737346</v>
+        <v>35.64716381972371</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.064029708868585</v>
+        <v>1.491502242807952</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4117766085772416</v>
+        <v>-0.1667180595534246</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6163</v>
+        <v>6279</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>393.8380620056482</v>
+        <v>558.2339961290573</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>43.3</v>
+        <v>127</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.83257002002662</v>
+        <v>57.36330548122854</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.58435840139506</v>
+        <v>15.99076969775305</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3501319006439303</v>
+        <v>0.6218522680812315</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2866547032570856</v>
+        <v>-0.2363843415077564</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6227</v>
+        <v>6234</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>391.9745330145391</v>
+        <v>549.4035175615226</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>113</v>
+        <v>36.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>42.62766745040317</v>
+        <v>50.97575092780348</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.53080062410892</v>
+        <v>19.28136970552135</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.054870709294181</v>
+        <v>1.064029708868585</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6635121858485432</v>
+        <v>0.4117766084341503</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6442</v>
+        <v>6210</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>384.5979482790846</v>
+        <v>545.4953875249219</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1615</v>
+        <v>18.05</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.24637714399277</v>
+        <v>51.59323596044614</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.95431833788605</v>
+        <v>6.72579399666185</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.493409533669333</v>
+        <v>0.1085244745973179</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>17.52843645163279</v>
+        <v>0.1379442824626392</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6229</v>
+        <v>6176</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>383.3000374553882</v>
+        <v>539.6497943026907</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>24.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.34524013146724</v>
+        <v>55.60078511218778</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.68205950377573</v>
+        <v>28.39049534459661</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.762612414550255</v>
+        <v>0.7648251464042263</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0991587690144452</v>
+        <v>1.512156794819825</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6412</v>
+        <v>6442</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>376.360288894505</v>
+        <v>524.5979482790846</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>1615</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.21767055504127</v>
+        <v>57.24637714765949</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.10644298527706</v>
+        <v>19.95431842260925</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7415293581518918</v>
+        <v>0.493409533669333</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.443540842323328</v>
+        <v>17.5284364513467</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6184</v>
+        <v>6191</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>371.1568356212218</v>
+        <v>523.6417030215554</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>41.15</v>
+        <v>84.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>21.62858491618736</v>
+        <v>47.32909769007723</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.10473848119856</v>
+        <v>27.12982318175672</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.018218801074867</v>
+        <v>1.072282601449544</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.006847004746841</v>
+        <v>0.4153483641789073</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6270</v>
+        <v>6217</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>367.8605009579209</v>
+        <v>514.5316449997686</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>29.95</v>
+        <v>175</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.40322508293248</v>
+        <v>54.4050640115105</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.46827354533465</v>
+        <v>14.3169248385801</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7889084630381776</v>
+        <v>4.33486317435983</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.132156110709524</v>
+        <v>5.036421130948256</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6244</v>
+        <v>6419</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>366.0008243905912</v>
+        <v>511.7346347621678</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>24.4</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.43175601889502</v>
+        <v>52.10969395373316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.7927897377716</v>
+        <v>22.96352164327324</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8132732249174556</v>
+        <v>0.5543557108942232</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0455341167057048</v>
+        <v>-1.00367847335912</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6409</v>
+        <v>6163</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>359.4423663389936</v>
+        <v>508.8380620056466</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1030</v>
+        <v>43.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.00282509475455</v>
+        <v>51.83257002700586</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.82458603953884</v>
+        <v>16.58435845672161</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9133591150753484</v>
+        <v>0.3501319006439303</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.908216477448301</v>
+        <v>0.2866547031903113</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6470</v>
+        <v>6416</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>359.4104136311823</v>
+        <v>507.2306052356462</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>41.5</v>
+        <v>100.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30.03800412225367</v>
+        <v>54.68491343197013</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>44.49327720108618</v>
+        <v>15.1867963214611</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.838312980571893</v>
+        <v>0.7120825074308554</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1677168333790377</v>
+        <v>0.0370771970913337</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6275</v>
+        <v>6206</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>355.5467219852067</v>
+        <v>506.017278775676</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>45.7</v>
+        <v>138.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.84932866837448</v>
+        <v>49.41402974067378</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.7208457549255</v>
+        <v>24.40432751315818</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9285922868864732</v>
+        <v>0.2602811957026558</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3662160488750076</v>
+        <v>-1.171154269410872</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6441</v>
+        <v>6472</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>354.7319013947222</v>
+        <v>505.9712675240604</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>21.25</v>
+        <v>435</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.35393956337096</v>
+        <v>53.23162664416971</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.79559484497857</v>
+        <v>30.01872851745603</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2287842697406492</v>
+        <v>0.6774247421735233</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0455670878242028</v>
+        <v>2.153630572922438</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6223</v>
+        <v>6239</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>352.0178342813626</v>
+        <v>502.5240041214908</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>5030</v>
+        <v>287</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38.99996869182381</v>
+        <v>54.69587392432123</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.49696131085538</v>
+        <v>12.54363381868858</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.720442525144879</v>
+        <v>1.505333872652589</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-87.89762703964971</v>
+        <v>3.128330801325927</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6177</v>
+        <v>6174</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>348.0789735296511</v>
+        <v>502.0400247298541</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>47.55</v>
+        <v>45.55</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.98412584385693</v>
+        <v>51.25242209473274</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.30949566943033</v>
+        <v>13.1425436253163</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5017343842174131</v>
+        <v>0.4193879097243387</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0896014490521822</v>
+        <v>0.5021054851866564</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6477</v>
+        <v>6229</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>347.1079109224706</v>
+        <v>498.3000374553882</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>37.05</v>
+        <v>24.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.52182334116729</v>
+        <v>52.34524010671304</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.29824582664845</v>
+        <v>13.68205961843794</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.93870330744171</v>
+        <v>1.762612414550255</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0820561911325131</v>
+        <v>0.099158768976287</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6261</v>
+        <v>6285</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>346.6161974133568</v>
+        <v>492.1137505009769</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.61462627794441</v>
+        <v>52.51176090198375</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>24.11080892504607</v>
+        <v>14.65286879096731</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.599697291418178</v>
+        <v>0.8739918625535201</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>1</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.8251722097627407</v>
+        <v>0.9593927143051753</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6285</v>
+        <v>6215</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>342.1137505009763</v>
+        <v>486.8117555807394</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>247</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.5117609128559</v>
+        <v>47.9050909004575</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.65286880017313</v>
+        <v>12.79690362966707</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8739918625535201</v>
+        <v>0.4480435428518663</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.9593927139235769</v>
+        <v>0.0109527284721078</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6182</v>
+        <v>6412</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>338.6366182498644</v>
+        <v>486.360288894505</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>110</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.13765272743972</v>
+        <v>47.21766971929527</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.81016665108128</v>
+        <v>25.10644343588547</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.213413776033681</v>
+        <v>0.7415293581518918</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.9265515078521238</v>
+        <v>0.4435408438496746</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6405</v>
+        <v>6409</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>333.3338712222049</v>
+        <v>474.4423663389936</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>40.25</v>
+        <v>1030</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.72265707437822</v>
+        <v>53.002825190858</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.54390258398169</v>
+        <v>19.82458602118435</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7389387444466331</v>
+        <v>0.9133591150753484</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.8259068597699337</v>
+        <v>2.908216468862542</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6432</v>
+        <v>6423</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>323.5462144049748</v>
+        <v>474.3245576878029</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.45570214660007</v>
+        <v>56.58319708117296</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.19116676537168</v>
+        <v>15.88745882708806</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6213561482179417</v>
+        <v>0.4078120710478514</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.7211590378078467</v>
+        <v>0.3414882727607014</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6194</v>
+        <v>6275</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>322.5908232948232</v>
+        <v>470.5467219852067</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>29.75</v>
+        <v>45.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.21827202448242</v>
+        <v>54.84932863837439</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.30738593648126</v>
+        <v>20.72084579254654</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1230707791896783</v>
+        <v>0.9285922868864732</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0918261252179387</v>
+        <v>0.3662160488273139</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6217</v>
+        <v>6277</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>314.5316449997685</v>
+        <v>468.4400460570678</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>175</v>
+        <v>79.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.40506400943818</v>
+        <v>48.89920816005505</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.31692475889225</v>
+        <v>36.65747056078165</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.33486317435983</v>
+        <v>0.4038342020930925</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5.036421131024584</v>
+        <v>-0.5406459143822298</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6167</v>
+        <v>6204</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>307.3855596769686</v>
+        <v>462.1224552186068</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.93181629537075</v>
+        <v>57.02079263841873</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.24282284221066</v>
+        <v>18.43084682448834</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.90282628172046</v>
+        <v>3.044500897357133</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0809255956632683</v>
+        <v>1.442245270708211</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6411</v>
+        <v>6261</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>303.5091746935789</v>
+        <v>461.6161974133568</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.09104576974312</v>
+        <v>46.61462628383838</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.83096258585797</v>
+        <v>24.11080893425862</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8576720603347204</v>
+        <v>0.599697291418178</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.7924503329776313</v>
+        <v>0.8251722097054945</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6266</v>
+        <v>6451</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>300.6321083486163</v>
+        <v>459.794120283499</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>25</v>
+        <v>453.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.37700214538894</v>
+        <v>52.91579407963987</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.33527041754093</v>
+        <v>10.69752324879238</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.013325201321883</v>
+        <v>1.234114533486751</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0514124334544068</v>
+        <v>6.255058279258984</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6233</v>
+        <v>6165</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>297.0458991394158</v>
+        <v>454.9291155775561</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21.8</v>
+        <v>48.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.97364237328794</v>
+        <v>48.34625601597563</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.08153097060021</v>
+        <v>10.020352810584</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7111792673913935</v>
+        <v>4.5193137618854</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1731308787126361</v>
+        <v>-0.0262505896384889</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6198</v>
+        <v>6182</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>288.4497852454349</v>
+        <v>453.6366182498644</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>19.4</v>
+        <v>110</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.37019903168825</v>
+        <v>49.13765273171512</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.795319858454928</v>
+        <v>12.81016681319543</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2859652996995775</v>
+        <v>1.213413776033681</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.162056472757117</v>
+        <v>0.9265515077185776</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6236</v>
+        <v>6405</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>283.6617050652613</v>
+        <v>448.3338712222049</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0</v>
+        <v>40.25</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.2661279169273</v>
+        <v>46.72265707833307</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.976568976137196</v>
+        <v>24.54390260199561</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0</v>
+        <v>0.7389387444466331</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2234751754226422</v>
+        <v>0.8259068597317736</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6451</v>
+        <v>6443</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>279.794120283499</v>
+        <v>441.263796666794</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>453.5</v>
+        <v>26.65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.91579407596211</v>
+        <v>45.86875085283518</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.69752315441651</v>
+        <v>13.22248971065428</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.234114533486751</v>
+        <v>1.222973149677565</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,51 +4280,51 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>6.255058280117531</v>
+        <v>0.285478607649539</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6288</v>
+        <v>6185</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>274.1623227954031</v>
+        <v>434.6997843927652</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>20.95</v>
+        <v>12.65</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.12010230369736</v>
+        <v>29.77127454081341</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v/>
+        <v>25.64379005599559</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.6182511143073882</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0137243745044277</v>
+        <v>-0.0662192696923839</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6414</v>
+        <v>6220</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>264.0002721951551</v>
+        <v>428.9261518403976</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>390</v>
+        <v>25.9</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>41.68839979028543</v>
+        <v>42.47451661581849</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.4106716409476</v>
+        <v>22.38136067317762</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4560360981553977</v>
+        <v>1.184980529164982</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-5.616624631806086</v>
+        <v>0.3039984579343147</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6417</v>
+        <v>6208</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>263.0502509771013</v>
+        <v>424.4245981761354</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>106</v>
+        <v>82.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>36.25788448581032</v>
+        <v>49.1625690339968</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.06731680536659</v>
+        <v>9.036185571307744</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4860053056529334</v>
+        <v>0.6379396716921866</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1162007515605383</v>
+        <v>0.4009681185554257</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6283</v>
+        <v>6464</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>258.9769870105815</v>
+        <v>421.1628433975877</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>20</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.04361467917883</v>
+        <v>43.23754746170833</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>30.73239472754121</v>
+        <v>30.36148990197136</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7993180288706967</v>
+        <v>0.0264456456029753</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0971779482326786</v>
+        <v>-0.0482342124952933</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6245</v>
+        <v>6462</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>254.5299629977683</v>
+        <v>420.5907742526043</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>83.2</v>
+        <v>101</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.64279509996974</v>
+        <v>50.89135699701958</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.27973762696614</v>
+        <v>12.23656185908324</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8440487803055989</v>
+        <v>1.209885155478894</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1500699578030893</v>
+        <v>0.6630354209547886</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6276</v>
+        <v>6411</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>250.6624404691856</v>
+        <v>418.5091746935789</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>20.25</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.01658479242569</v>
+        <v>50.09104578754207</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.49175526444076</v>
+        <v>14.83096272037524</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.122719002771823</v>
+        <v>0.8576720603347204</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2275014374274705</v>
+        <v>0.7924503328249972</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6246</v>
+        <v>6474</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>249.6520045124877</v>
+        <v>417.4166039771195</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>12.25</v>
+        <v>37.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.68750515171868</v>
+        <v>42.94906900445996</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.73803786984623</v>
+        <v>14.5241689530106</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2983311302048909</v>
+        <v>1.34166039771195</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.087105725225745</v>
+        <v>-0.130648497808718</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6443</v>
+        <v>6274</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>231.263796666794</v>
+        <v>412.270691863583</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>26.65</v>
+        <v>1490</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.86875087372697</v>
+        <v>51.12197072777106</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.22248963298686</v>
+        <v>12.9275383547691</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.222973149677565</v>
+        <v>0.9268584740680228</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.2854786076686182</v>
+        <v>-6.403204722301069</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6222</v>
+        <v>6233</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>209.2952005868291</v>
+        <v>412.0458991394159</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>20.05</v>
+        <v>21.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.33754290463593</v>
+        <v>50.97364242445797</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9.04375991103098</v>
+        <v>15.08153110002304</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3632252586844889</v>
+        <v>0.7111792673913935</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3958481005208724</v>
+        <v>0.1731308785981609</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>167.3930883486433</v>
+        <v>391.9745330145391</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.24634457150348</v>
+        <v>42.62766747683354</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.793237500110434</v>
+        <v>10.53080069090993</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.0115692307692307</v>
+        <v>4.054870709294181</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.5313049805255357</v>
+        <v>-0.6635121864591017</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6188</v>
+        <v>6230</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>110.3490826174812</v>
+        <v>375.2775820448347</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>68.8</v>
+        <v>109.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.93803173043239</v>
+        <v>46.82584921352677</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>18.60514702148712</v>
+        <v>16.46054862653324</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6140222457569217</v>
+        <v>0.3191825275895955</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,62 +4863,1864 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1391087176259233</v>
+        <v>0.7010345810442833</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
+        <v>6184</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>大豐電</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>371.1568356212217</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>21.62858504467857</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>24.1047384770022</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>2.018218801074867</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.0068470047659198</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>倍微</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>367.8605009579209</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>47.4032250554932</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>9.468273628387887</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.7889084630381776</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.1321561106713652</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6244</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>茂迪</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>366.0008243905912</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>47.43175598904953</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>16.79278979938342</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.8132732249174556</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.0455341167152452</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>365.6624404691856</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>50.01658483581895</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>22.49175519755269</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.122719002771823</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.2275014373511542</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6470</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>359.4104136311823</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30.03800419715256</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>44.49327725936715</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.838312980571893</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.1677168332073242</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6441</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>廣錠</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>354.7319013947222</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46.35393933994581</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>20.79559493140837</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.2287842697406492</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-0.0455670879005233</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6223</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>352.0178342813625</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>5030</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>38.9999686992475</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>17.49696137486963</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.720442525144879</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-87.89762704537287</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6477</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>安集</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>347.1079109224706</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>51.52182334116729</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>19.29824598107766</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.93870330744171</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.08205619103711891</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6243</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>迅杰</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>346.8379694901398</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>43.92432158434628</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>21.2090351087599</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.4606680362319315</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.5406676145234499</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6177</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>達麗</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>338.0789735296511</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>48.98412575844604</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>22.30949574290134</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.5017343842174131</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.08960144907125479</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6432</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>今展科</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>323.5462144049748</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>43.45570215743621</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>13.19116680677185</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.6213561482179417</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.7211590378460142</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6417</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>韋僑</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>323.0502509771013</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>36.25788938084183</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>25.06731810614524</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.4860053056529334</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.1162007347324562</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6194</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>育富</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>322.5908232948266</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>45.21827193834459</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>23.30738594996907</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.1230707791896783</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.091826125208398</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6167</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>307.3855596769686</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>51.93181632637274</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>14.2428228706723</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.90282628172046</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.0809255956142205</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6266</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>泰詠</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>300.6321083486163</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>49.37700206967062</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>11.33527041754093</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.013325201321883</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0514124334448678</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>居易</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>299.0954287072032</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30.98047134370266</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>15.43879036807052</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.751714035294688</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.1303103565697171</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>華孚</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>292.4308618822029</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>50.48633896518344</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>11.94375592219526</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.8620575388160414</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.168532247697453</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>瑞築</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>288.449785245435</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>51.37019902941866</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>5.795319864271846</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.2859652996995775</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0.1620564727857384</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>283.6617050652613</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>47.2661279169273</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>9.976568976137196</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.2234751754226422</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6166</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>凌華</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>277.1593420469347</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>40.18774923401491</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>16.0057026831725</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.2644741930982675</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-1.38059478188315</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6288</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>聯嘉</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>274.0471752455182</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>44.27768280025433</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.6831032524092705</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.0001777997045697</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6192</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>272.2169587081626</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>53.18838914962472</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>17.49532048531762</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.6777259341108275</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.1858453671130503</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6414</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>樺漢</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>264.000272195155</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>41.68839984156633</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>18.41067164462857</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.4560360981553977</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-5.616624633236999</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6283</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>淳安</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>258.9769870105815</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>41.0436144156709</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>30.73239478918075</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.7993180288706967</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.09717794830899119</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6245</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>立端</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>254.5299629977683</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>51.64279509651434</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>11.27973774058665</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.8440487803055989</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.1500699579938741</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6246</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>臺龍</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>249.6520045124877</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>41.68750514349114</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>20.73803792389728</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.2983311302048909</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.08710572520666519</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6196</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>246.3320983970804</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>46.35469722723465</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10.82515177948724</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.7224885999903564</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.430773301370043</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>209.2952005868292</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>51.33754290729333</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>9.043760229337751</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.3632252586844889</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.3958481003682375</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6282</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>康舒</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>200.683556533685</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>43.84051228508066</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>16.59063793626193</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.5836815785156393</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.1561752820433253</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>亞弘電</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>197.719000118224</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>32.4094327591086</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>26.45979967487279</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.549272636931833</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.0410440365497395</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>167.3930883486433</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>39.24634457736374</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>7.793237481868392</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.0115692307692307</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.5313049806495507</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6281</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>全國電</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>143.6758945885842</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>45.3761794119614</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>13.36509818383952</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4511383446854565</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0152093138145796</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6189</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>138.8188304744297</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46.97933704989992</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>8.456451046218756</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.753849095804886</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0650838819815556</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6188</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>廣明</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>110.349082617479</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>43.93803172578775</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>18.60514704211912</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6140222457569217</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.1391087175305305</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>79.69256883947179</v>
-      </c>
-      <c r="E84" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>79.69256883947182</v>
+      </c>
+      <c r="E118" s="2" t="n">
         <v>59.6</v>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30.58572186742816</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>17.3651698807019</v>
-      </c>
-      <c r="J84" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30.58572192743976</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>17.3651699188606</v>
+      </c>
+      <c r="J118" s="2" t="n">
         <v>0.5193246202755211</v>
       </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>0.1237877631542381</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.1237877629252934</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
